--- a/data/trans_orig/Q20C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización</t>
+          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,84</t>
+          <t>1,69; 16,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,8</t>
+          <t>4,5; 14,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,24</t>
+          <t>5,24; 14,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 17,16</t>
+          <t>3,62; 16,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,78</t>
+          <t>1,76; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,92</t>
+          <t>2,38; 4,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,51</t>
+          <t>3,41; 12,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 22,01</t>
+          <t>4,04; 19,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,87</t>
+          <t>2,45; 8,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,0</t>
+          <t>3,84; 8,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,58</t>
+          <t>5,16; 11,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 14,48</t>
+          <t>4,42; 14,62</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,49</t>
+          <t>1,82; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,98</t>
+          <t>2,93; 11,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,86</t>
+          <t>3,45; 9,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,24</t>
+          <t>3,37; 12,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,15</t>
+          <t>2,78; 5,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,35</t>
+          <t>4,84; 10,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,89</t>
+          <t>3,34; 7,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,3</t>
+          <t>2,52; 4,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,04</t>
+          <t>2,84; 4,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,01</t>
+          <t>4,86; 9,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,55</t>
+          <t>3,96; 7,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,79</t>
+          <t>3,13; 7,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,66</t>
+          <t>3,61; 8,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,4</t>
+          <t>2,31; 4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,41</t>
+          <t>2,48; 8,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 15,54</t>
+          <t>2,3; 16,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,5</t>
+          <t>2,68; 6,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,92</t>
+          <t>3,34; 10,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,87</t>
+          <t>3,74; 7,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,83</t>
+          <t>3,26; 14,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,86</t>
+          <t>3,5; 6,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,35</t>
+          <t>3,14; 7,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,25</t>
+          <t>3,74; 7,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 12,67</t>
+          <t>3,12; 13,26</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 25,83</t>
+          <t>5,02; 24,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,87</t>
+          <t>2,9; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 37,83</t>
+          <t>5,11; 39,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 13,57</t>
+          <t>5,98; 14,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,94</t>
+          <t>3,19; 10,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,6</t>
+          <t>3,45; 8,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,93</t>
+          <t>4,59; 11,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,83</t>
+          <t>3,57; 7,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,29</t>
+          <t>4,96; 15,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,68</t>
+          <t>3,57; 6,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 17,85</t>
+          <t>5,84; 18,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,21</t>
+          <t>5,13; 9,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,93</t>
+          <t>4,97; 11,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,47</t>
+          <t>4,05; 7,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,64</t>
+          <t>5,52; 13,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,62</t>
+          <t>5,24; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,43; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,96</t>
+          <t>4,43; 6,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,18</t>
+          <t>4,89; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,23</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,61</t>
+          <t>4,39; 7,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,76</t>
+          <t>4,52; 6,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,91</t>
+          <t>5,83; 10,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,54</t>
+          <t>5,18; 8,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,22</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 16,78</t>
+          <t>1,7; 16,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 14,89</t>
+          <t>4,96; 15,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 14,83</t>
+          <t>5,08; 15,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,05</t>
+          <t>3,24; 16,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,85</t>
+          <t>1,93; 6,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,92</t>
+          <t>2,5; 5,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,11</t>
+          <t>3,65; 12,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 19,84</t>
+          <t>4,07; 20,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,67</t>
+          <t>2,6; 8,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,85</t>
+          <t>4,0; 9,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,6</t>
+          <t>5,34; 12,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 14,62</t>
+          <t>4,39; 13,32</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>6,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,72</t>
+          <t>1,63; 4,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 11,62</t>
+          <t>2,76; 11,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,49</t>
+          <t>3,54; 8,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 12,19</t>
+          <t>4,92; 15,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,9</t>
+          <t>2,86; 5,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,07</t>
+          <t>4,99; 9,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,93</t>
+          <t>3,24; 7,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,31</t>
+          <t>2,54; 4,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,93</t>
+          <t>2,79; 5,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,21</t>
+          <t>4,56; 8,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,4</t>
+          <t>3,96; 7,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,6</t>
+          <t>4,23; 11,08</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,74</t>
+          <t>3,59; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,3</t>
+          <t>2,33; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,45</t>
+          <t>2,41; 8,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 16,58</t>
+          <t>2,18; 15,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,53</t>
+          <t>2,62; 6,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,4</t>
+          <t>3,52; 10,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,62</t>
+          <t>3,8; 7,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 14,62</t>
+          <t>4,24; 14,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,7</t>
+          <t>3,36; 6,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,0</t>
+          <t>3,15; 7,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,06</t>
+          <t>3,64; 7,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 13,26</t>
+          <t>3,83; 12,12</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,69</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 24,02</t>
+          <t>5,43; 22,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,0</t>
+          <t>2,73; 4,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 39,64</t>
+          <t>4,97; 37,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,09</t>
+          <t>5,89; 13,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,97</t>
+          <t>2,99; 11,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,88</t>
+          <t>3,43; 8,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,08</t>
+          <t>4,54; 11,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,64</t>
+          <t>3,73; 7,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 15,04</t>
+          <t>4,93; 14,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,47</t>
+          <t>3,63; 6,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 18,74</t>
+          <t>5,96; 18,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,44</t>
+          <t>5,06; 9,13</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,84</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,96</t>
+          <t>4,87; 12,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,61</t>
+          <t>4,02; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,84</t>
+          <t>5,33; 14,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,0</t>
+          <t>5,57; 10,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,95</t>
+          <t>3,41; 6,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,99</t>
+          <t>4,41; 6,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,87</t>
+          <t>4,92; 8,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,51; 8,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,92</t>
+          <t>4,36; 7,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,61</t>
+          <t>4,61; 6,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,25</t>
+          <t>5,74; 9,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,7</t>
+          <t>5,44; 8,69</t>
         </is>
       </c>
     </row>
